--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_337_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_337_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1761</v>
+        <v>5.9393</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7687</v>
+        <v>4.036</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4074</v>
+        <v>1.9033</v>
       </c>
       <c r="G2" t="n">
         <v>4.9464</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0022</v>
+        <v>-0.239</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8566</v>
+        <v>-0.5893</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8545</v>
+        <v>0.3504</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8738</v>
+        <v>3.937</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7107</v>
+        <v>3.6058</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1631</v>
+        <v>0.3312</v>
       </c>
       <c r="G3" t="n">
         <v>2.8022</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7727000000000001</v>
+        <v>-0.1641</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4708</v>
+        <v>0.3659</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.698</v>
+        <v>-0.53</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7886</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6677</v>
+        <v>3.5283</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1234</v>
+        <v>2.6306</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5444</v>
+        <v>0.8976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3532</v>
+        <v>2.639</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3732</v>
+        <v>0.0961</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02</v>
+        <v>2.5429</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1937</v>
+        <v>2.5676</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9935</v>
+        <v>0.2857</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7998</v>
+        <v>2.2819</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8404</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6203</v>
+        <v>-0.1896</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7798</v>
+        <v>0.261</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5311</v>
+        <v>0.1032</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0703</v>
+        <v>0.063</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6014</v>
+        <v>0.0402</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.335</v>
+        <v>2.9959</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2021</v>
+        <v>2.3546</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1329</v>
+        <v>0.6413</v>
       </c>
       <c r="G5" t="n">
-        <v>2.639</v>
+        <v>1.2711</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0961</v>
+        <v>0.2305</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5429</v>
+        <v>1.0406</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5676</v>
+        <v>1.8395</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2857</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2819</v>
+        <v>1.2514</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.5684</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1896</v>
+        <v>-0.3577</v>
       </c>
       <c r="O5" t="n">
-        <v>0.261</v>
+        <v>-0.2108</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0901</v>
+        <v>0.3126</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3655</v>
+        <v>0.5151</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2754</v>
+        <v>-0.2025</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>0.2525</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2826</v>
+        <v>2.8741</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7085</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5741000000000001</v>
+        <v>2.3091</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2711</v>
+        <v>0.3532</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2305</v>
+        <v>0.3732</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0406</v>
+        <v>-0.02</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8395</v>
+        <v>1.1937</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5881999999999999</v>
+        <v>1.9935</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2514</v>
+        <v>-0.7998</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5684</v>
+        <v>-0.8404</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3577</v>
+        <v>-1.6203</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2108</v>
+        <v>0.7798</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>2.7834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5992</v>
+        <v>-0.2625</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8689</v>
+        <v>-0.6286</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2697</v>
+        <v>0.3662</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.1919</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9492</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9245</v>
+        <v>1.9917</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9022</v>
@@ -1000,13 +1000,13 @@
         <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8004</v>
+        <v>-0.5838</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8566</v>
+        <v>-0.7073</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0562</v>
+        <v>0.1235</v>
       </c>
       <c r="V7" t="n">
         <v>2.2862</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1008</v>
+        <v>-0.1942</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2519</v>
+        <v>-1.1772</v>
       </c>
       <c r="F8" t="n">
-        <v>1.151</v>
+        <v>0.983</v>
       </c>
       <c r="G8" t="n">
         <v>0.0963</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4266</v>
+        <v>0.3332</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4208</v>
+        <v>0.4955</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0057</v>
+        <v>-0.1623</v>
       </c>
       <c r="V8" t="n">
         <v>0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7658</v>
+        <v>-1.0245</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5654</v>
+        <v>-1.8577</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7996</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7264</v>
@@ -1156,13 +1156,13 @@
         <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.127</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3655</v>
+        <v>0.3422</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2385</v>
+        <v>0.2721</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0654</v>
+        <v>-3.6532</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5784</v>
+        <v>-4.535</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4871</v>
+        <v>0.8818</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9305</v>
+        <v>-3.8705</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7732</v>
+        <v>-2.7563</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1573</v>
+        <v>-1.1142</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.5228</v>
+        <v>-3.8057</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.004</v>
+        <v>-1.1253</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5188</v>
+        <v>-2.6804</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4077</v>
+        <v>-0.0649</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7692</v>
+        <v>-1.631</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3615</v>
+        <v>1.5662</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9004</v>
+        <v>-0.8885</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2696</v>
+        <v>-0.892</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6308</v>
+        <v>0.0035</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3943</v>
+        <v>2.0336</v>
       </c>
       <c r="W10" t="n">
-        <v>1.214</v>
+        <v>3.6419</v>
       </c>
       <c r="X10" t="n">
         <v>-1.6083</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2406</v>
+        <v>-4.3366</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5847</v>
+        <v>-3.1184</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3441</v>
+        <v>-1.2182</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8705</v>
+        <v>-3.9305</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.7563</v>
+        <v>-3.7732</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1142</v>
+        <v>-0.1573</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8057</v>
+        <v>-3.5228</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1253</v>
+        <v>-3.004</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.6804</v>
+        <v>-0.5188</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0649</v>
+        <v>-0.4077</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.631</v>
+        <v>-0.7692</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5662</v>
+        <v>0.3615</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4759</v>
+        <v>-1.1716</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9417</v>
+        <v>-0.8096</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5342</v>
+        <v>-0.362</v>
       </c>
       <c r="V11" t="n">
-        <v>2.0336</v>
+        <v>-0.3943</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6419</v>
+        <v>1.214</v>
       </c>
       <c r="X11" t="n">
         <v>-1.6083</v>
@@ -1345,37 +1345,37 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.1379</v>
+        <v>11.258</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5838000000000001</v>
+        <v>1.703799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>9.553999999999998</v>
+        <v>9.554</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6786000000000012</v>
+        <v>0.6785999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>-6.3985</v>
       </c>
       <c r="I12" t="n">
-        <v>7.077000000000002</v>
+        <v>7.076999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>4.952900000000001</v>
+        <v>4.9529</v>
       </c>
       <c r="K12" t="n">
-        <v>3.598799999999998</v>
+        <v>3.598799999999999</v>
       </c>
       <c r="L12" t="n">
         <v>1.3541</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.274299999999999</v>
+        <v>-4.2743</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.997400000000001</v>
+        <v>-9.997399999999999</v>
       </c>
       <c r="O12" t="n">
         <v>5.723000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>19.7161</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.066400000000001</v>
+        <v>-1.9461</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.9653</v>
+        <v>-1.8451</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.101</v>
+        <v>-0.1009</v>
       </c>
       <c r="V12" t="n">
         <v>3.2476</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0678</v>
+        <v>3.2593</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1654</v>
+        <v>2.4577</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9025</v>
+        <v>0.8016</v>
       </c>
       <c r="G13" t="n">
         <v>2.519</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7112000000000001</v>
+        <v>-0.0973</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8259</v>
+        <v>0.1182</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1147</v>
+        <v>-0.2155</v>
       </c>
       <c r="V13" t="n">
         <v>0.1418</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7936</v>
+        <v>1.5848</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5937</v>
+        <v>1.9532</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1999</v>
+        <v>-0.3683</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8493000000000001</v>
+        <v>1.8563</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.442</v>
+        <v>-0.2518</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2913</v>
+        <v>2.1081</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3188</v>
+        <v>2.6644</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7064</v>
+        <v>0.2353</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6124</v>
+        <v>2.4291</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4695</v>
+        <v>-0.8081</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1484</v>
+        <v>-0.487</v>
       </c>
       <c r="O14" t="n">
         <v>-0.3211</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.5515</v>
+        <v>-0.4639</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6891</v>
+        <v>0.0147</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3181</v>
+        <v>-0.2473</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0072</v>
+        <v>0.2621</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6468</v>
+        <v>-1.214</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4975</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2903</v>
+        <v>1.3747</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9505</v>
+        <v>1.0685</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3398</v>
+        <v>0.3062</v>
       </c>
       <c r="G15" t="n">
         <v>0.9314</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>0.127</v>
+        <v>0.2113</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U15" t="n">
-        <v>0.351</v>
+        <v>0.3174</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4846</v>
+        <v>1.273</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2455</v>
+        <v>1.7117</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7608</v>
+        <v>-0.4387</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8563</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2518</v>
+        <v>-0.442</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1081</v>
+        <v>1.2913</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6644</v>
+        <v>2.3188</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2353</v>
+        <v>0.7064</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4291</v>
+        <v>1.6124</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8081</v>
+        <v>-1.4695</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.487</v>
+        <v>-1.1484</v>
       </c>
       <c r="O16" t="n">
         <v>-0.3211</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0855</v>
+        <v>1.1685</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.955</v>
+        <v>-0.2001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1305</v>
+        <v>1.3687</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.214</v>
+        <v>0.6468</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>-1.4975</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1741</v>
+        <v>-0.129</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3056</v>
+        <v>-0.5415</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4797</v>
+        <v>0.4124</v>
       </c>
       <c r="G17" t="n">
         <v>1.5384</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1149</v>
+        <v>0.8118</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4129</v>
+        <v>0.177</v>
       </c>
       <c r="U17" t="n">
-        <v>0.702</v>
+        <v>0.6348</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7326</v>
+        <v>-0.9242</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4496</v>
+        <v>-0.5184</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.283</v>
+        <v>-0.4058</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3007</v>
+        <v>-0.823</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.4382</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5793</v>
+        <v>-0.3848</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5821</v>
+        <v>-0.2118</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6351</v>
+        <v>-0.2486</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.947</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7186</v>
+        <v>-0.6112</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0862</v>
+        <v>-0.1896</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6323</v>
+        <v>-0.4216</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6403</v>
+        <v>-0.3332</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1325</v>
+        <v>-0.0747</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5078</v>
+        <v>-0.2585</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1151</v>
+        <v>-1.0685</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5184</v>
+        <v>-1.1374</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5967</v>
+        <v>0.0689</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.823</v>
+        <v>-0.1574</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4382</v>
+        <v>0.1069</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3848</v>
+        <v>-0.2643</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2118</v>
+        <v>0.2857</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2486</v>
+        <v>0.2857</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6112</v>
+        <v>-0.4431</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1896</v>
+        <v>-0.1788</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4216</v>
+        <v>-0.2643</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5241</v>
+        <v>-0.2153</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0747</v>
+        <v>-0.0314</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4494</v>
+        <v>-0.1838</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3774</v>
+        <v>-1.1195</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2554</v>
+        <v>-0.7917</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.122</v>
+        <v>-0.3278</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1574</v>
+        <v>0.4782</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1069</v>
+        <v>1.6459</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2643</v>
+        <v>-1.1677</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2857</v>
+        <v>0.6752</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2857</v>
+        <v>2.1006</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.4255</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4431</v>
+        <v>-0.1969</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1788</v>
+        <v>-0.4547</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2643</v>
+        <v>0.2578</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5241</v>
+        <v>0.7244</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>-0.1294</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3747</v>
+        <v>0.8538</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2476</v>
+        <v>-1.3566</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6174</v>
+        <v>-1.2753</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6302</v>
+        <v>-0.0813</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4782</v>
+        <v>-2.3007</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6459</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1677</v>
+        <v>-1.5793</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6752</v>
+        <v>-1.5821</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1006</v>
+        <v>-0.6351</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4255</v>
+        <v>-0.947</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1969</v>
+        <v>-0.7186</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4547</v>
+        <v>-0.0862</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2578</v>
+        <v>-0.6323</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4037</v>
+        <v>1.0163</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.955</v>
+        <v>0.3068</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5513</v>
+        <v>0.7095</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9304</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3486</v>
+        <v>-2.0448</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1557</v>
+        <v>-2.6839</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8072</v>
+        <v>0.6391</v>
       </c>
       <c r="G22" t="n">
         <v>2.1789</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5601</v>
+        <v>0.8639</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6168</v>
+        <v>-0.145</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1769</v>
+        <v>1.0089</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5187</v>
+        <v>-4.4458</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0595</v>
+        <v>-5.1774</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.7317</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3167</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0602</v>
+        <v>0.0127</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3383</v>
+        <v>0.2203</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3984</v>
+        <v>-0.2076</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6778999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6084</v>
+        <v>-5.755</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6115</v>
+        <v>-4.0833</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.997</v>
+        <v>-1.6717</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4323</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1788</v>
+        <v>-0.3253</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6844</v>
+        <v>0.2126</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8632</v>
+        <v>-0.5379</v>
       </c>
       <c r="V24" t="n">
         <v>0.3943</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.138</v>
+        <v>-9.351599999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.017999999999999</v>
+        <v>-9.017800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1198</v>
+        <v>-0.3336999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6785999999999985</v>
       </c>
       <c r="H25" t="n">
-        <v>6.3986</v>
+        <v>6.398599999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.077099999999999</v>
+        <v>-7.0771</v>
       </c>
       <c r="J25" t="n">
         <v>4.274400000000001</v>
@@ -2383,10 +2383,10 @@
         <v>9.997299999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.722999999999999</v>
+        <v>-5.723000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.952800000000001</v>
+        <v>-4.952800000000002</v>
       </c>
       <c r="N25" t="n">
         <v>-3.5986</v>
@@ -2404,19 +2404,19 @@
         <v>10.4381</v>
       </c>
       <c r="S25" t="n">
-        <v>3.0662</v>
+        <v>3.8525</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1010000000000001</v>
+        <v>0.1009</v>
       </c>
       <c r="U25" t="n">
-        <v>2.9653</v>
+        <v>3.7519</v>
       </c>
       <c r="V25" t="n">
         <v>-3.2477</v>
       </c>
       <c r="W25" t="n">
-        <v>6.322500000000001</v>
+        <v>6.3225</v>
       </c>
       <c r="X25" t="n">
         <v>-9.5701</v>
